--- a/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="172">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -150,7 +150,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -918,47 +921,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -968,52 +971,52 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +1031,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1048,7 +1051,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1063,7 +1066,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1078,7 +1081,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1098,12 +1101,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1118,212 +1121,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1338,12 +1341,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1358,7 +1361,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1378,127 +1381,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1756,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1769,6 +1772,11 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1783,7 +1791,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1793,57 +1801,57 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1853,7 +1861,7 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -1863,7 +1871,7 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -1873,57 +1881,57 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1938,7 +1946,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1948,7 +1956,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1963,7 +1971,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1973,7 +1981,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +1996,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1998,47 +2006,47 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -2048,52 +2056,52 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2108,37 +2116,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2153,37 +2161,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="148">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -150,175 +150,103 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+    <t>All symbols have nets.</t>
+  </si>
+  <si>
+    <t>Shorted Inputs</t>
+  </si>
+  <si>
+    <t>No Shorted Input Nets found.</t>
+  </si>
+  <si>
+    <t>Shorted Outputs</t>
+  </si>
+  <si>
+    <t>No Shorted Output Nets found.</t>
+  </si>
+  <si>
+    <t>Floating Inputs</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XU1</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraREGISTER.scli(scli)</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraREGISTER.sdapd_registermap(pd0)</t>
+  </si>
+  <si>
+    <t>No Connects - Outputs</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE</t>
+  </si>
+  <si>
+    <t>CELBG83021 - {"path": "XU1,XceleraCORE,XSERVICE", "instance": "XSERVICE", "symbol": "CELBG83021", "io": "output", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>pd0 - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdapd_registermap", "io": "output", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>No Connects - Inputs</t>
   </si>
   <si>
     <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
   </si>
   <si>
-    <t>XU9,SIMPV</t>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
   </si>
   <si>
     <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
   </si>
   <si>
-    <t>XU1,XceleraCORE,XU19,XLDOFIXED</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOFIXED1</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOUNITY</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPFIXEDlow</t>
-  </si>
-  <si>
-    <t>XU1,SIMPV</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPFIXEDmedium</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPOPENhigh</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPOPENlow</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPOPENmedium</t>
-  </si>
-  <si>
-    <t>Shorted Inputs</t>
-  </si>
-  <si>
-    <t>No Shorted Input Nets found.</t>
-  </si>
-  <si>
-    <t>Shorted Outputs</t>
-  </si>
-  <si>
-    <t>No Shorted Output Nets found.</t>
-  </si>
-  <si>
-    <t>Floating Inputs</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDO1.factory_ldooutput(30)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDO1.factory_ldooutput(29)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDO1.factory_ldooutput(28)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOCONFIGURE1.enable_ldo(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOFIXED.enable_ldo(114)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOSTANDALONE.enable_ldo(116)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOUNITY.enable_ldo(119)</t>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>114 - {"path": "XU1,XceleraCORE,XU19,XLDOFIXED", "instance": "XLDOFIXED", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>116 - {"path": "XU1,XceleraCORE,XU19,XLDOSTANDALONE", "instance": "XLDOSTANDALONE", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XU1,XceleraCORE,XU19,XLDOUNITY", "instance": "XLDOUNITY", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>XU1,XceleraRING</t>
   </si>
   <si>
-    <t>Floating pin XCELINA.ten_taext(ten_taext)</t>
-  </si>
-  <si>
-    <t>Floating pin XCELIND.ten_tdext(ten_tdext)</t>
-  </si>
-  <si>
-    <t>XU1</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.scli(scli)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE</t>
-  </si>
-  <si>
-    <t>Floating pin XSERVICE.CELBG83021(CELBG83021)</t>
-  </si>
-  <si>
-    <t>Floating pin XCELIND.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.sdapd_registermap(pd0)</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>CELBG83021 - {"path": "XU1,XceleraCORE,XSERVICE", "instance": "XSERVICE", "symbol": "CELBG83021", "io": "output", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XU1,XceleraRING,XCELIND", "instance": "XCELIND", "symbol": "tdext", "io": "output", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>pd0 - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdapd_registermap", "io": "output", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>114 - {"path": "XU1,XceleraCORE,XU19,XLDOFIXED", "instance": "XLDOFIXED", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>116 - {"path": "XU1,XceleraCORE,XU19,XLDOSTANDALONE", "instance": "XLDOSTANDALONE", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XU1,XceleraCORE,XU19,XLDOUNITY", "instance": "XLDOUNITY", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
     <t>ten_taext - {"path": "XU1,XceleraRING,XCELINA", "instance": "XCELINA", "symbol": "ten_taext", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>ten_tdext - {"path": "XU1,XceleraRING,XCELIND", "instance": "XCELIND", "symbol": "ten_tdext", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>scli - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "scli", "io": "input", "bus": "", "type": "child"}</t>
@@ -916,52 +844,52 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -971,52 +899,47 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>71</v>
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +954,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1051,7 +974,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1066,7 +989,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1004,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1101,12 +1024,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1121,212 +1044,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1341,12 +1264,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1361,7 +1284,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1381,127 +1304,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1756,7 +1679,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1774,11 +1697,6 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1786,12 +1704,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1801,137 +1719,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1946,7 +1734,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1956,7 +1744,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1971,7 +1759,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1981,7 +1769,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1991,12 +1779,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2006,102 +1794,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2111,42 +1819,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2156,42 +1844,32 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="141">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -207,30 +207,6 @@
     <t>No Connects - Inputs</t>
   </si>
   <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
     <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
@@ -247,6 +223,9 @@
   </si>
   <si>
     <t>ten_taext - {"path": "XU1,XceleraRING,XCELINA", "instance": "XCELINA", "symbol": "ten_taext", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>tmi - {"path": "XU1,XceleraCORE", "instance": "XceleraCORE", "symbol": "tmi", "io": "inout", "bus": "[4:0]", "type": "child"}</t>
   </si>
   <si>
     <t>scli - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "scli", "io": "input", "bus": "", "type": "child"}</t>
@@ -844,7 +823,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -854,92 +833,57 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -954,7 +898,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -974,7 +918,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -989,7 +933,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1004,7 +948,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1024,12 +968,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1044,212 +988,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1264,12 +1208,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1284,7 +1228,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1304,127 +1248,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="144">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -96,6 +96,9 @@
     <t>Xdatamap4 (datamap.code) missing expected field datamap_code_2</t>
   </si>
   <si>
+    <t>XUSERVICEreference dftprobe_description total_bits:3 cannot be 'text'</t>
+  </si>
+  <si>
     <t>XU1,XceleraCORE,XU19</t>
   </si>
   <si>
@@ -186,6 +189,9 @@
     <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
   </si>
   <si>
+    <t>Floating pin XceleraRING.unlock(unlock)</t>
+  </si>
+  <si>
     <t>Floating Outputs</t>
   </si>
   <si>
@@ -232,6 +238,9 @@
   </si>
   <si>
     <t>sdai - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdai", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>unlock - {"path": "XU1,XceleraRING", "instance": "XceleraRING", "symbol": "unlock", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -823,67 +832,72 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +912,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -918,7 +932,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -933,7 +947,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +962,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -968,12 +982,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -988,212 +1002,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1208,12 +1222,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1242,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1248,127 +1262,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1467,12 +1481,12 @@
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1512,73 +1526,73 @@
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>6</v>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>6</v>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>6</v>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>22</v>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -1598,7 +1612,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -1614,6 +1628,11 @@
     <row r="54" spans="1:1">
       <c r="A54" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1628,7 +1647,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1638,7 +1657,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1653,7 +1672,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1663,7 +1682,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1678,7 +1697,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1688,7 +1707,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1703,7 +1722,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1713,7 +1732,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1723,12 +1742,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1738,22 +1757,27 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1768,17 +1792,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1793,27 +1817,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="168">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -171,31 +171,26 @@
     <t>Shorted Outputs</t>
   </si>
   <si>
-    <t>No Shorted Output Nets found.</t>
+    <t xml:space="preserve">-------------------------------------------------- Shorted OUTPUTS (!!! MUST FIX !!! - not allowed) --------------------------------------------------
+</t>
+  </si>
+  <si>
+    <t>XU1</t>
+  </si>
+  <si>
+    <t>Shorted output PORB97836 XceleraREGISTER.PORB97836 --&gt; XceleraSERDES.PORB97836(PORB97836)</t>
   </si>
   <si>
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XU1</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.scli(scli)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraRING.unlock(unlock)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XceleraREGISTER.sdapd_registermap(pd0)</t>
+    <t>No Floating Output Nets found.</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
@@ -207,12 +202,63 @@
     <t>CELBG83021 - {"path": "XU1,XceleraCORE,XSERVICE", "instance": "XSERVICE", "symbol": "CELBG83021", "io": "output", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>pd0 - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdapd_registermap", "io": "output", "bus": "", "type": "child"}</t>
+    <t>XU1,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>scli - {"path": "XU1,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "scli", "io": "output", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>tdext - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_register - {"path": "XU1,XceleraSERDES,XSERDESinputSINGLEregister", "instance": "XSERDESinputSINGLEregister", "symbol": "scl_register", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_register - {"path": "XU1,XceleraSERDES,XSERDESinputSINGLEregister", "instance": "XSERDESinputSINGLEregister", "symbol": "sda_register", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
   </si>
   <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
+  </si>
+  <si>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
+  </si>
+  <si>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
     <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
@@ -231,16 +277,43 @@
     <t>ten_taext - {"path": "XU1,XceleraRING,XCELINA", "instance": "XCELINA", "symbol": "ten_taext", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>tmi - {"path": "XU1,XceleraCORE", "instance": "XceleraCORE", "symbol": "tmi", "io": "inout", "bus": "[4:0]", "type": "child"}</t>
-  </si>
-  <si>
-    <t>scli - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "scli", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>sdai - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdai", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>unlock - {"path": "XU1,XceleraRING", "instance": "XceleraRING", "symbol": "unlock", "io": "input", "bus": "", "type": "child"}</t>
+    <t>sdai - {"path": "XU1,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "sdai", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_done - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_bistok - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_bistok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_programdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -832,72 +905,157 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>64</v>
+      <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>66</v>
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -912,7 +1070,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -932,7 +1090,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -947,7 +1105,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1120,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -982,12 +1140,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1002,212 +1160,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1222,12 +1380,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1242,7 +1400,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1262,127 +1420,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -1717,12 +1875,47 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1732,52 +1925,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1792,17 +1940,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1812,32 +1960,72 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Post Verilog Run Checks.xlsx
@@ -9,29 +9,27 @@
   <sheets>
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
-    <sheet name="Missing Bio Symbol Files" sheetId="3" r:id="rId3"/>
-    <sheet name="Missing Nets" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Inputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Shorted Outputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Inputs" sheetId="7" r:id="rId7"/>
-    <sheet name="Floating Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Outputs" sheetId="9" r:id="rId9"/>
-    <sheet name="No Connects - Inputs" sheetId="10" r:id="rId10"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="11" r:id="rId11"/>
-    <sheet name="Ring Core IO check report" sheetId="12" r:id="rId12"/>
-    <sheet name="D to A Tree" sheetId="13" r:id="rId13"/>
-    <sheet name="Symbol Length Exceed Max" sheetId="14" r:id="rId14"/>
-    <sheet name="Cell Length Exceed Max 50" sheetId="15" r:id="rId15"/>
-    <sheet name="All Nestos have Verilog File" sheetId="16" r:id="rId16"/>
-    <sheet name="Zero Length Verilog Files" sheetId="17" r:id="rId17"/>
-    <sheet name="Verilog Checker" sheetId="18" r:id="rId18"/>
+    <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
+    <sheet name="Shorted Nets" sheetId="4" r:id="rId4"/>
+    <sheet name="Floating Inputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Outputs" sheetId="6" r:id="rId6"/>
+    <sheet name="No Connects - Customer" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Celera" sheetId="8" r:id="rId8"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="9" r:id="rId9"/>
+    <sheet name="Ring Core IO check report" sheetId="10" r:id="rId10"/>
+    <sheet name="D to A Tree" sheetId="11" r:id="rId11"/>
+    <sheet name="Symbol Length Exceed Max" sheetId="12" r:id="rId12"/>
+    <sheet name="Cell Length Exceed Max 50" sheetId="13" r:id="rId13"/>
+    <sheet name="All Nestos have Verilog File" sheetId="14" r:id="rId14"/>
+    <sheet name="Zero Length Verilog Files" sheetId="15" r:id="rId15"/>
+    <sheet name="Verilog Checker" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="323">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -150,170 +148,634 @@
     <t>Xdatamap1 (datamap.function) missing expected field datamap_function_7</t>
   </si>
   <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
     <t>Missing Nets</t>
   </si>
   <si>
     <t>All symbols have nets.</t>
   </si>
   <si>
-    <t>Shorted Inputs</t>
-  </si>
-  <si>
-    <t>No Shorted Input Nets found.</t>
-  </si>
-  <si>
-    <t>Shorted Outputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-------------------------------------------------- Shorted OUTPUTS (!!! MUST FIX !!! - not allowed) --------------------------------------------------
-</t>
+    <t>Shorted Nets</t>
+  </si>
+  <si>
+    <t>ERROR: Net CELBG83021 - Shorted outputs (XSERVICE.CELBG83021 --&gt; XU2.CELBG --&gt; XU4.CELBG --&gt; XU10.CELBG --&gt; XU19.CELBG)(CELBG83021)</t>
   </si>
   <si>
     <t>XU1</t>
   </si>
   <si>
-    <t>Shorted output PORB97836 XceleraREGISTER.PORB97836 --&gt; XceleraSERDES.PORB97836(PORB97836)</t>
+    <t>ERROR: Net PORB97836 - Shorted outputs (XceleraCORE.PORB97836 --&gt; XceleraREGISTER.PORB97836 --&gt; XceleraSERDES.PORB97836)(PORB97836)</t>
   </si>
   <si>
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>Floating pin XLDOCONFIGURE1.enable_ldo(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XLDOFIXED.enable_ldo(114)</t>
+  </si>
+  <si>
+    <t>Floating pin XLDOSTANDALONE.enable_ldo(116)</t>
+  </si>
+  <si>
+    <t>Floating pin XLDOUNITY.enable_ldo(119)</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE</t>
+  </si>
+  <si>
+    <t>Floating pin XSERVICE.CELBG83021(CELBG83021)</t>
+  </si>
+  <si>
+    <t>XU1,XceleraRING</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraRING.tmi(tmi[5])</t>
+  </si>
+  <si>
+    <t>Floating pin XCELINA.ten_taext(ten_taext)</t>
+  </si>
+  <si>
+    <t>Floating pin XCELIND.ten_tdext(ten_tdext)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE</t>
-  </si>
-  <si>
-    <t>CELBG83021 - {"path": "XU1,XceleraCORE,XSERVICE", "instance": "XSERVICE", "symbol": "CELBG83021", "io": "output", "bus": "", "type": "child"}</t>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>XU23.KELVIN_CN net: 152 io: inout</t>
+  </si>
+  <si>
+    <t>XU12.KELVIN_CN net: 165 io: inout</t>
+  </si>
+  <si>
+    <t>XWRAPregister_LDOconfigurationA_xdatamap1_d6b88199_0.o net: 76 io: output</t>
+  </si>
+  <si>
+    <t>XWRAPregister_LDOconfigurationA_xdatamap1_d6b88199_1.o net: 77 io: output</t>
+  </si>
+  <si>
+    <t>XWRAPregister_LDOconfigurationA_xdatamap1_d6b88199_2.o net: 78 io: output</t>
+  </si>
+  <si>
+    <t>XWRAPregister_LDOconfigurationA_xdatamap1_d6b88199_3.o net: 79 io: output</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XSERVICE,XBYPASS</t>
+  </si>
+  <si>
+    <t>dft_hex0x01.ten net: noconn_dft_hex0x01_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x01.ten net: noconn_dft_hex0x01_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x01.ten net: noconn_dft_hex0x01_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x01.ten net: noconn_dft_hex0x01_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x01.ten net: noconn_dft_hex0x01_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x01.ten net: noconn_dft_hex0x01_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x01.ten net: noconn_dft_hex0x01_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOconfigNO1</t>
+  </si>
+  <si>
+    <t>dft_hex0x07.ten net: noconn_dft_hex0x07_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x07.ten net: noconn_dft_hex0x07_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x07.ten net: noconn_dft_hex0x07_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x07.ten net: noconn_dft_hex0x07_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x07.ten net: noconn_dft_hex0x07_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x07.ten net: noconn_dft_hex0x07_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x07.ten net: noconn_dft_hex0x07_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
+  </si>
+  <si>
+    <t>dft_hex0x08.ten net: noconn_dft_hex0x08_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x08.ten net: noconn_dft_hex0x08_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x08.ten net: noconn_dft_hex0x08_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x08.ten net: noconn_dft_hex0x08_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x08.ten net: noconn_dft_hex0x08_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x08.ten net: noconn_dft_hex0x08_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x08.ten net: noconn_dft_hex0x08_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
+  </si>
+  <si>
+    <t>dft_hex0x09.ten net: noconn_dft_hex0x09_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x09.ten net: noconn_dft_hex0x09_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x09.ten net: noconn_dft_hex0x09_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x09.ten net: noconn_dft_hex0x09_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x09.ten net: noconn_dft_hex0x09_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x09.ten net: noconn_dft_hex0x09_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x09.ten net: noconn_dft_hex0x09_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOFIXED</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A.ten net: noconn_dft_hex0x0A_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A.ten net: noconn_dft_hex0x0A_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A.ten net: noconn_dft_hex0x0A_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A.ten net: noconn_dft_hex0x0A_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A.ten net: noconn_dft_hex0x0A_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A.ten net: noconn_dft_hex0x0A_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A.ten net: noconn_dft_hex0x0A_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOFIXED1</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B.ten net: noconn_dft_hex0x0B_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B.ten net: noconn_dft_hex0x0B_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B.ten net: noconn_dft_hex0x0B_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B.ten net: noconn_dft_hex0x0B_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B.ten net: noconn_dft_hex0x0B_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B.ten net: noconn_dft_hex0x0B_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B.ten net: noconn_dft_hex0x0B_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOSTANDALONE</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C.ten net: noconn_dft_hex0x0C_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C.ten net: noconn_dft_hex0x0C_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C.ten net: noconn_dft_hex0x0C_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C.ten net: noconn_dft_hex0x0C_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C.ten net: noconn_dft_hex0x0C_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C.ten net: noconn_dft_hex0x0C_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C.ten net: noconn_dft_hex0x0C_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D.ten net: noconn_dft_hex0x0D_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D.ten net: noconn_dft_hex0x0D_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D.ten net: noconn_dft_hex0x0D_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D.ten net: noconn_dft_hex0x0D_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D.ten net: noconn_dft_hex0x0D_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D.ten net: noconn_dft_hex0x0D_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D.ten net: noconn_dft_hex0x0D_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOUNITY</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E.ten net: noconn_dft_hex0x0E_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E.ten net: noconn_dft_hex0x0E_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E.ten net: noconn_dft_hex0x0E_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E.ten net: noconn_dft_hex0x0E_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E.ten net: noconn_dft_hex0x0E_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E.ten net: noconn_dft_hex0x0E_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E.ten net: noconn_dft_hex0x0E_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x10.ten net: noconn_dft_hex0x10_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x10.ten net: noconn_dft_hex0x10_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x10.ten net: noconn_dft_hex0x10_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x10.ten net: noconn_dft_hex0x10_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x10.ten net: noconn_dft_hex0x10_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x10.ten net: noconn_dft_hex0x10_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x10.ten net: noconn_dft_hex0x10_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x11.ten net: noconn_dft_hex0x11_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x11.ten net: noconn_dft_hex0x11_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x11.ten net: noconn_dft_hex0x11_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x11.ten net: noconn_dft_hex0x11_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x11.ten net: noconn_dft_hex0x11_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x11.ten net: noconn_dft_hex0x11_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x11.ten net: noconn_dft_hex0x11_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x12.ten net: noconn_dft_hex0x12_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x12.ten net: noconn_dft_hex0x12_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x12.ten net: noconn_dft_hex0x12_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x12.ten net: noconn_dft_hex0x12_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x12.ten net: noconn_dft_hex0x12_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x12.ten net: noconn_dft_hex0x12_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x12.ten net: noconn_dft_hex0x12_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPFIXEDlow</t>
+  </si>
+  <si>
+    <t>dft_hex0x13.ten net: noconn_dft_hex0x13_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x13.ten net: noconn_dft_hex0x13_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x13.ten net: noconn_dft_hex0x13_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x13.ten net: noconn_dft_hex0x13_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x13.ten net: noconn_dft_hex0x13_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x13.ten net: noconn_dft_hex0x13_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x13.ten net: noconn_dft_hex0x13_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPFIXEDmedium</t>
+  </si>
+  <si>
+    <t>dft_hex0x14.ten net: noconn_dft_hex0x14_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x14.ten net: noconn_dft_hex0x14_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x14.ten net: noconn_dft_hex0x14_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x14.ten net: noconn_dft_hex0x14_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x14.ten net: noconn_dft_hex0x14_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x14.ten net: noconn_dft_hex0x14_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x14.ten net: noconn_dft_hex0x14_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPOPENhigh</t>
+  </si>
+  <si>
+    <t>dft_hex0x15.ten net: noconn_dft_hex0x15_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x15.ten net: noconn_dft_hex0x15_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x15.ten net: noconn_dft_hex0x15_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x15.ten net: noconn_dft_hex0x15_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x15.ten net: noconn_dft_hex0x15_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x15.ten net: noconn_dft_hex0x15_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x15.ten net: noconn_dft_hex0x15_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPOPENlow</t>
+  </si>
+  <si>
+    <t>dft_hex0x16.ten net: noconn_dft_hex0x16_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x16.ten net: noconn_dft_hex0x16_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x16.ten net: noconn_dft_hex0x16_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x16.ten net: noconn_dft_hex0x16_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x16.ten net: noconn_dft_hex0x16_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x16.ten net: noconn_dft_hex0x16_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x16.ten net: noconn_dft_hex0x16_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPOPENmedium</t>
+  </si>
+  <si>
+    <t>dft_hex0x17.ten net: noconn_dft_hex0x17_ten_1 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x17.ten net: noconn_dft_hex0x17_ten_2 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x17.ten net: noconn_dft_hex0x17_ten_3 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x17.ten net: noconn_dft_hex0x17_ten_4 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x17.ten net: noconn_dft_hex0x17_ten_5 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x17.ten net: noconn_dft_hex0x17_ten_6 io: output</t>
+  </si>
+  <si>
+    <t>dft_hex0x17.ten net: noconn_dft_hex0x17_ten_7 io: output</t>
+  </si>
+  <si>
+    <t>XceleraSERVICE.ok_ibias net: noconn io: output</t>
+  </si>
+  <si>
+    <t>XU1,XceleraREGISTER</t>
+  </si>
+  <si>
+    <t>XREG0x10.register net: REG0x10_3 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x10.register net: REG0x10_4 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x10.register net: REG0x10_5 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x10.register net: REG0x10_6 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x10.register net: REG0x10_7 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x11.register net: REG0x11_3 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x11.register net: REG0x11_4 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x11.register net: REG0x11_5 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x11.register net: REG0x11_6 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x11.register net: REG0x11_7 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x12.register net: REG0x12_3 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x12.register net: REG0x12_4 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x12.register net: REG0x12_5 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x12.register net: REG0x12_6 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x12.register net: REG0x12_7 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x13.register net: REG0x13_3 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x13.register net: REG0x13_4 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x13.register net: REG0x13_5 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x13.register net: REG0x13_6 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x13.register net: REG0x13_7 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x14.register net: REG0x14_0 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x14.register net: REG0x14_1 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x14.register net: REG0x14_5 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x14.register net: REG0x14_6 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x14.register net: REG0x14_7 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x15.register net: REG0x15_5 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x15.register net: REG0x15_6 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x21.register net: REG0x21_3 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x21.register net: REG0x21_4 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x21.register net: REG0x21_5 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x21.register net: REG0x21_6 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x22.register net: REG0x22_0 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x22.register net: REG0x22_1 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x22.register net: REG0x22_2 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x22.register net: REG0x22_7 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x45.register net: REG0x45_0 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x45.register net: REG0x45_1 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x45.register net: REG0x45_2 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x45.register net: REG0x45_6 io: output</t>
+  </si>
+  <si>
+    <t>XREG0x45.register net: REG0x45_7 io: output</t>
   </si>
   <si>
     <t>XU1,XceleraSERDES</t>
   </si>
   <si>
-    <t>scli - {"path": "XU1,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "scli", "io": "output", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_register - {"path": "XU1,XceleraSERDES,XSERDESinputSINGLEregister", "instance": "XSERDESinputSINGLEregister", "symbol": "scl_register", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_register - {"path": "XU1,XceleraSERDES,XSERDESinputSINGLEregister", "instance": "XSERDESinputSINGLEregister", "symbol": "sda_register", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>114 - {"path": "XU1,XceleraCORE,XU19,XLDOFIXED", "instance": "XLDOFIXED", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>116 - {"path": "XU1,XceleraCORE,XU19,XLDOSTANDALONE", "instance": "XLDOSTANDALONE", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XU1,XceleraCORE,XU19,XLDOUNITY", "instance": "XLDOUNITY", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>XU1,XceleraRING</t>
-  </si>
-  <si>
-    <t>ten_taext - {"path": "XU1,XceleraRING,XCELINA", "instance": "XCELINA", "symbol": "ten_taext", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>sdai - {"path": "XU1,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "sdai", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_done - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_bistok - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_bistok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_programdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
+    <t>XSERDESdftYesYes.tdo net: tdo_noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDESdftYesYes.ten_serdes net: ten_serdes_noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDESdftYesYes.ten_oscillator_on net: ten_oscillator_on_noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDESdftYesYes.ten_oscillator_off net: ten_oscillator_off_noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDESdftYesYes.tdext net: tdext_noconn_noconn_noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDESdftYesYes.ten_oscillator_div8 net: ten_oscillator_div8_noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDESdftYesYes.ten_oscillator_external net: ten_oscillator_external_noconn io: output</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -905,157 +1367,27 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>68</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>93</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -1070,7 +1402,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1085,27 +1417,17 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>96</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -1115,17 +1437,217 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -1140,12 +1662,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>99</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -1155,217 +1677,17 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>140</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1375,172 +1697,132 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>144</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>147</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>148</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>149</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>150</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>151</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>152</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>153</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>154</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>156</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>157</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>158</v>
+        <v>313</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>160</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>161</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>162</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>163</v>
+        <v>318</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>164</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>165</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -1825,7 +2107,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1835,12 +2117,22 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1850,12 +2142,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1865,7 +2157,62 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1875,32 +2222,67 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>47</v>
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1910,22 +2292,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1935,22 +2347,947 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -1960,72 +3297,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
